--- a/Samples_Export/RealSchool_v1_ideal.xlsx
+++ b/Samples_Export/RealSchool_v1_ideal.xlsx
@@ -52,7 +52,7 @@
     <x:t>Математика · Математика·10</x:t>
   </x:si>
   <x:si>
-    <x:t>Информатика · Информатика·10·2 / Информатика · Информатика·10</x:t>
+    <x:t>Информатика · Информатика·10 / Информатика · Информатика·10·2</x:t>
   </x:si>
   <x:si>
     <x:t>ДМП · ДМП·10·2 / ДМП · ДМП·10</x:t>
@@ -61,66 +61,66 @@
     <x:t>Урок 2</x:t>
   </x:si>
   <x:si>
+    <x:t>Химия (проф) · Химия (проф)·10 / История Беларуси (проф) · История Беларуси (проф)·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Биология (база) · Биология (база)·10 / История Беларуси (база) · История Беларуси (база)·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Физическая культура и здоровье · Физическая культура и здоровье·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Биология (проф) · Биология (проф)·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Черчение · Черчение·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Урок 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Обществоведение (проф) · Обществоведение (проф)·10 / Биология (проф) · Биология (проф)·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Русский язык · Русский язык·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Белорусский язык · Белорусский язык·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>География · География·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Урок 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Физика · Физика·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Обществоведение (база) · Обществоведение (база)·10 / Биология (база) · Биология (база)·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Английский язык · Английский язык·10 / Английский язык · Английский язык·10·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Урок 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>История Беларуси (база) · История Беларуси (база)·10 / Химия (база) · Химия (база)·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Английский язык · Английский язык·10·2 / Английский язык · Английский язык·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Биология (проф) · Биология (проф)·10 / Химия (база) · Химия (база)·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Урок 6</x:t>
+  </x:si>
+  <x:si>
     <x:t>История Беларуси (проф) · История Беларуси (проф)·10 / Химия (проф) · Химия (проф)·10</x:t>
   </x:si>
   <x:si>
-    <x:t>История Беларуси (база) · История Беларуси (база)·10 / Биология (база) · Биология (база)·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Физическая культура и здоровье · Физическая культура и здоровье·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Биология (проф) · Биология (проф)·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Черчение · Черчение·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Урок 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Биология (проф) · Биология (проф)·10 / Обществоведение (проф) · Обществоведение (проф)·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Русский язык · Русский язык·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Белорусский язык · Белорусский язык·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>География · География·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Урок 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Физика · Физика·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Биология (база) · Биология (база)·10 / Обществоведение (база) · Обществоведение (база)·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Английский язык · Английский язык·10 / Английский язык · Английский язык·10·2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Урок 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Химия (проф) · Химия (проф)·10 / История Беларуси (проф) · История Беларуси (проф)·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Обществоведение (проф) · Обществоведение (проф)·10 / Биология (проф) · Биология (проф)·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>История Беларуси (база) · История Беларуси (база)·10 / Химия (база) · Химия (база)·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Биология (проф) · Биология (проф)·10 / Химия (база) · Химия (база)·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Урок 6</x:t>
-  </x:si>
-  <x:si>
     <x:t>Урок 7</x:t>
   </x:si>
   <x:si>
@@ -139,18 +139,15 @@
     <x:t>Химия · Химия·10</x:t>
   </x:si>
   <x:si>
+    <x:t>История РБ в контексте мировой истории · История РБ в контексте мировой истории·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Английский язык · Английский язык·10</x:t>
+  </x:si>
+  <x:si>
     <x:t>Биология · Биология·10</x:t>
   </x:si>
   <x:si>
-    <x:t>Информатика · Информатика·10 / Информатика · Информатика·10·2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>История РБ в контексте мировой истории · История РБ в контексте мировой истории·10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Английский язык · Английский язык·10</x:t>
-  </x:si>
-  <x:si>
     <x:t>Обществоведение · Обществоведение·10</x:t>
   </x:si>
   <x:si>
@@ -187,36 +184,39 @@
     <x:t>Физика · Физика·11</x:t>
   </x:si>
   <x:si>
+    <x:t>Английский язык (проф) · Английский язык (проф)·11 / Биология (проф) · Биология (проф)·11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Химия (проф) · Химия (проф)·11 / Обществоведение (проф) · Обществоведение (проф)·11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Математика · Математика·11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Биология (проф) · Биология (проф)·11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Английский язык (база) · Английский язык (база)·11 / Английский язык (проф) · Английский язык (проф)·11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Биология (база) · Биология (база)·11 / Химия (проф) · Химия (проф)·11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Английский язык (проф) · Английский язык (проф)·11 / Английский язык (база) · Английский язык (база)·11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Русский язык · Русский язык·11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Информатика · Информатика·11 / Информатика · Информатика·11·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Астрономия · Астрономия·11</x:t>
+  </x:si>
+  <x:si>
     <x:t>Биология (проф) · Биология (проф)·11 / Английский язык (проф) · Английский язык (проф)·11</x:t>
   </x:si>
   <x:si>
-    <x:t>Обществоведение (проф) · Обществоведение (проф)·11 / Химия (проф) · Химия (проф)·11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Математика · Математика·11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Биология (проф) · Биология (проф)·11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Английский язык (проф) · Английский язык (проф)·11 / Английский язык (база) · Английский язык (база)·11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Биология (база) · Биология (база)·11 / Химия (проф) · Химия (проф)·11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Русский язык · Русский язык·11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика · Информатика·11 / Информатика · Информатика·11·2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Астрономия · Астрономия·11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Английский язык (проф) · Английский язык (проф)·11 / Биология (проф) · Биология (проф)·11</x:t>
-  </x:si>
-  <x:si>
     <x:t>География · География·11</x:t>
   </x:si>
   <x:si>
@@ -229,7 +229,7 @@
     <x:t>Биология · Биология·11</x:t>
   </x:si>
   <x:si>
-    <x:t>Английский язык · Английский язык·11 / Английский язык · Английский язык·11·2</x:t>
+    <x:t>Английский язык · Английский язык·11·2 / Английский язык · Английский язык·11</x:t>
   </x:si>
   <x:si>
     <x:t>Химия · Химия·11</x:t>
@@ -247,63 +247,63 @@
     <x:t>Белорусская литература · Белорусская литература·5</x:t>
   </x:si>
   <x:si>
+    <x:t>Белорусский язык · Белорусский язык·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Искусство · Искусство·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Всемирная история · Всемирная история·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Физическая культура и здоровье · Физическая культура и здоровье·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Русский язык · Русский язык·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Математика · Математика·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Английский язык · Английский язык·5·2 / Английский язык · Английский язык·5</x:t>
+  </x:si>
+  <x:si>
     <x:t>Русская литература · Русская литература·5</x:t>
   </x:si>
   <x:si>
-    <x:t>Искусство · Искусство·5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Всемирная история · Всемирная история·5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Физическая культура и здоровье · Физическая культура и здоровье·5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Русский язык · Русский язык·5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Математика · Математика·5</x:t>
+    <x:t>Человек и мир · Человек и мир·5</x:t>
   </x:si>
   <x:si>
     <x:t>Английский язык · Английский язык·5 / Английский язык · Английский язык·5·2</x:t>
   </x:si>
   <x:si>
-    <x:t>Белорусский язык · Белорусский язык·5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Английский язык · Английский язык·5·2 / Английский язык · Английский язык·5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Человек и мир · Человек и мир·5</x:t>
-  </x:si>
-  <x:si>
     <x:t>Основы безопасности жизнедеятельности · Основы безопасности жизнедеятельности·5</x:t>
   </x:si>
   <x:si>
+    <x:t>Трудовое обучение · Трудовое обучение·5 / Трудовое обучение · Трудовое обучение·5·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Класс 5Б · 1-я смена</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Классный час · Классный руководитель·5Б</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Класс 5В · 1-я смена</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Классный час · Классный руководитель·5В</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Класс 5Г · 1-я смена</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Классный час · Классный руководитель·5Г</x:t>
+  </x:si>
+  <x:si>
     <x:t>Трудовое обучение · Трудовое обучение·5·2 / Трудовое обучение · Трудовое обучение·5</x:t>
   </x:si>
   <x:si>
-    <x:t>Класс 5Б · 1-я смена</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Классный час · Классный руководитель·5Б</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Трудовое обучение · Трудовое обучение·5 / Трудовое обучение · Трудовое обучение·5·2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Класс 5В · 1-я смена</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Классный час · Классный руководитель·5В</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Класс 5Г · 1-я смена</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Классный час · Классный руководитель·5Г</x:t>
-  </x:si>
-  <x:si>
     <x:t>Класс 6А · 2-я смена</x:t>
   </x:si>
   <x:si>
@@ -340,25 +340,28 @@
     <x:t>История Беларуси · История Беларуси·6</x:t>
   </x:si>
   <x:si>
+    <x:t>Трудовое обучение · Трудовое обучение·6 / Трудовое обучение · Трудовое обучение·6·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Английский язык · Английский язык·6 / Английский язык · Английский язык·6·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Русская литература · Русская литература·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Информатика · Информатика·6·2 / Информатика · Информатика·6</x:t>
+  </x:si>
+  <x:si>
     <x:t>Трудовое обучение · Трудовое обучение·6·2 / Трудовое обучение · Трудовое обучение·6</x:t>
   </x:si>
   <x:si>
-    <x:t>Английский язык · Английский язык·6 / Английский язык · Английский язык·6·2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Русская литература · Русская литература·6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика · Информатика·6·2 / Информатика · Информатика·6</x:t>
-  </x:si>
-  <x:si>
     <x:t>Английский язык · Английский язык·6·2 / Английский язык · Английский язык·6</x:t>
   </x:si>
   <x:si>
     <x:t>Класс 6Б · 2-я смена</x:t>
   </x:si>
   <x:si>
-    <x:t>Трудовое обучение · Трудовое обучение·6 / Трудовое обучение · Трудовое обучение·6·2</x:t>
+    <x:t>Информатика · Информатика·6 / Информатика · Информатика·6·2</x:t>
   </x:si>
   <x:si>
     <x:t>Классный час · Классный руководитель·6Б</x:t>
@@ -376,9 +379,6 @@
     <x:t>Классный час · Классный руководитель·6Г</x:t>
   </x:si>
   <x:si>
-    <x:t>Информатика · Информатика·6 / Информатика · Информатика·6·2</x:t>
-  </x:si>
-  <x:si>
     <x:t>Класс 7А · 2-я смена</x:t>
   </x:si>
   <x:si>
@@ -415,39 +415,39 @@
     <x:t>Русский язык · Русский язык·7</x:t>
   </x:si>
   <x:si>
+    <x:t>Трудовое обучение · Трудовое обучение·7·2 / Трудовое обучение · Трудовое обучение·7</x:t>
+  </x:si>
+  <x:si>
     <x:t>Биология · Биология·7</x:t>
   </x:si>
   <x:si>
     <x:t>Английский язык · Английский язык·7 / Английский язык · Английский язык·7·2</x:t>
   </x:si>
   <x:si>
+    <x:t>Информатика · Информатика·7·2 / Информатика · Информатика·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Физика · Физика·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Химия · Химия·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Белорусская литература · Белорусская литература·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Русская литература · Русская литература·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Класс 7Б · 2-я смена</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Классный час · Классный руководитель·7Б</x:t>
+  </x:si>
+  <x:si>
     <x:t>Информатика · Информатика·7 / Информатика · Информатика·7·2</x:t>
   </x:si>
   <x:si>
-    <x:t>Физика · Физика·7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Химия · Химия·7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Белорусская литература · Белорусская литература·7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Русская литература · Русская литература·7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Класс 7Б · 2-я смена</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Классный час · Классный руководитель·7Б</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Трудовое обучение · Трудовое обучение·7·2 / Трудовое обучение · Трудовое обучение·7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика · Информатика·7·2 / Информатика · Информатика·7</x:t>
-  </x:si>
-  <x:si>
     <x:t>Класс 7В · 2-я смена</x:t>
   </x:si>
   <x:si>
@@ -472,69 +472,69 @@
     <x:t>Биология · Биология·8</x:t>
   </x:si>
   <x:si>
+    <x:t>Трудовое обучение · Трудовое обучение·8 / Трудовое обучение · Трудовое обучение·8·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Всемирная история · Всемирная история·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Математика · Математика·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Информатика · Информатика·8 / Информатика · Информатика·8·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Химия · Химия·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Русский язык · Русский язык·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Физика · Физика·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>География · География·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Белорусская литература · Белорусская литература·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>История Беларуси · История Беларуси·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Белорусский язык · Белорусский язык·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Физическая культура и здоровье · Физическая культура и здоровье·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Английский язык · Английский язык·8·2 / Английский язык · Английский язык·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Русская литература · Русская литература·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Английский язык · Английский язык·8 / Английский язык · Английский язык·8·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Класс 8Б · 1-я смена</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Классный час · Классный руководитель·8Б</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Искусство · Искусство·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Класс 8В · 1-я смена</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Классный час · Классный руководитель·8В</x:t>
+  </x:si>
+  <x:si>
     <x:t>Трудовое обучение · Трудовое обучение·8·2 / Трудовое обучение · Трудовое обучение·8</x:t>
   </x:si>
   <x:si>
-    <x:t>Всемирная история · Всемирная история·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Математика · Математика·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика · Информатика·8 / Информатика · Информатика·8·2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Химия · Химия·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Русский язык · Русский язык·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Физика · Физика·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>География · География·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Белорусская литература · Белорусская литература·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>История Беларуси · История Беларуси·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Белорусский язык · Белорусский язык·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Физическая культура и здоровье · Физическая культура и здоровье·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Английский язык · Английский язык·8·2 / Английский язык · Английский язык·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Английский язык · Английский язык·8 / Английский язык · Английский язык·8·2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Русская литература · Русская литература·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Класс 8Б · 1-я смена</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Классный час · Классный руководитель·8Б</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Искусство · Искусство·8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Трудовое обучение · Трудовое обучение·8 / Трудовое обучение · Трудовое обучение·8·2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Класс 8В · 1-я смена</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Классный час · Классный руководитель·8В</x:t>
-  </x:si>
-  <x:si>
     <x:t>Информатика · Информатика·8·2 / Информатика · Информатика·8</x:t>
   </x:si>
   <x:si>
@@ -571,55 +571,55 @@
     <x:t>Математика · Математика·9</x:t>
   </x:si>
   <x:si>
+    <x:t>Английский язык · Английский язык·9·2 / Английский язык · Английский язык·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Физика · Физика·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Информатика · Информатика·9 / Информатика · Информатика·9·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Белорусский язык · Белорусский язык·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Всемирная история · Всемирная история·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>История Беларуси · История Беларуси·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Белорусская литература · Белорусская литература·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Искусство · Искусство·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Обществоведение · Обществоведение·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Трудовое обучение · Трудовое обучение·9·2 / Трудовое обучение · Трудовое обучение·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Класс 9Б · 1-я смена</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Классный час · Классный руководитель·9Б</x:t>
+  </x:si>
+  <x:si>
     <x:t>Английский язык · Английский язык·9 / Английский язык · Английский язык·9·2</x:t>
   </x:si>
   <x:si>
-    <x:t>Физика · Физика·9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика · Информатика·9 / Информатика · Информатика·9·2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Белорусский язык · Белорусский язык·9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Всемирная история · Всемирная история·9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>История Беларуси · История Беларуси·9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Белорусская литература · Белорусская литература·9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Искусство · Искусство·9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Обществоведение · Обществоведение·9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Английский язык · Английский язык·9·2 / Английский язык · Английский язык·9</x:t>
+    <x:t>Информатика · Информатика·9·2 / Информатика · Информатика·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Класс 9В · 1-я смена</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Классный час · Классный руководитель·9В</x:t>
   </x:si>
   <x:si>
     <x:t>Трудовое обучение · Трудовое обучение·9 / Трудовое обучение · Трудовое обучение·9·2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Класс 9Б · 1-я смена</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Классный час · Классный руководитель·9Б</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика · Информатика·9·2 / Информатика · Информатика·9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Класс 9В · 1-я смена</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Классный час · Классный руководитель·9В</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Трудовое обучение · Трудовое обучение·9·2 / Трудовое обучение · Трудовое обучение·9</x:t>
   </x:si>
   <x:si>
     <x:t>Класс 9Г · 1-я смена</x:t>
@@ -1894,24 +1894,24 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="E9" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="F9" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
       <x:c r="A10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>21</x:v>
@@ -1920,7 +1920,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>10</x:v>
@@ -1937,7 +1937,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
         <x:v>36</x:v>
@@ -2002,7 +2002,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>21</x:v>
@@ -2022,10 +2022,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
@@ -2033,7 +2033,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>10</x:v>
@@ -2053,7 +2053,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>25</x:v>
@@ -2070,7 +2070,7 @@
     </x:row>
     <x:row r="20" spans="1:6">
       <x:c r="A20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>10</x:v>
@@ -2079,13 +2079,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
@@ -2093,18 +2093,18 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
       <x:c r="A23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
@@ -2132,19 +2132,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C25" s="0" t="s">
+      <x:c r="D25" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D25" s="0" t="s">
+      <x:c r="E25" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E25" s="0" t="s">
+      <x:c r="F25" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -2152,19 +2152,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C26" s="0" t="s">
+      <x:c r="D26" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D26" s="0" t="s">
+      <x:c r="E26" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6">
@@ -2172,19 +2172,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C27" s="0" t="s">
+      <x:c r="D27" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
+      <x:c r="F27" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
@@ -2192,19 +2192,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
+      <x:c r="F28" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
@@ -2212,30 +2212,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
       <x:c r="A30" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>62</x:v>
@@ -2244,7 +2244,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -2252,7 +2252,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>64</x:v>
@@ -2308,19 +2308,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
@@ -2328,19 +2328,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -2354,13 +2354,13 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
@@ -2368,36 +2368,36 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
       <x:c r="A40" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>66</x:v>
@@ -2411,10 +2411,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
         <x:v>72</x:v>
@@ -2499,7 +2499,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:6">
@@ -2507,16 +2507,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
         <x:v>75</x:v>
@@ -2527,13 +2527,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
         <x:v>86</x:v>
@@ -2544,7 +2544,7 @@
     </x:row>
     <x:row r="50" spans="1:6">
       <x:c r="A50" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>81</x:v>
@@ -2597,7 +2597,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
         <x:v>81</x:v>
@@ -2611,16 +2611,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
         <x:v>81</x:v>
@@ -2631,7 +2631,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>77</x:v>
@@ -2654,13 +2654,13 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
         <x:v>79</x:v>
@@ -2674,18 +2674,18 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
       <x:c r="A60" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>75</x:v>
@@ -2694,7 +2694,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -2710,7 +2710,7 @@
     </x:row>
     <x:row r="63" spans="1:6">
       <x:c r="A63" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:6">
@@ -2738,7 +2738,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>79</x:v>
@@ -2752,7 +2752,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>81</x:v>
@@ -2764,7 +2764,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6">
@@ -2772,7 +2772,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>80</x:v>
@@ -2792,7 +2792,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>79</x:v>
@@ -2801,7 +2801,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
         <x:v>81</x:v>
@@ -2812,24 +2812,24 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:6">
       <x:c r="A70" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>79</x:v>
@@ -2841,7 +2841,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:6">
@@ -2849,12 +2849,12 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:6">
       <x:c r="A73" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:6">
@@ -2882,10 +2882,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>80</x:v>
@@ -2894,7 +2894,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:6">
@@ -2905,10 +2905,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
         <x:v>77</x:v>
@@ -2925,10 +2925,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
         <x:v>81</x:v>
@@ -2942,7 +2942,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>81</x:v>
@@ -2954,7 +2954,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:6">
@@ -2965,13 +2965,13 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="D79" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E79" s="0" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
         <x:v>78</x:v>
@@ -2979,7 +2979,7 @@
     </x:row>
     <x:row r="80" spans="1:6">
       <x:c r="A80" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>82</x:v>
@@ -3112,7 +3112,7 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
         <x:v>99</x:v>
@@ -3120,16 +3120,16 @@
     </x:row>
     <x:row r="90" spans="1:6">
       <x:c r="A90" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
         <x:v>100</x:v>
@@ -3145,7 +3145,7 @@
     </x:row>
     <x:row r="93" spans="1:6">
       <x:c r="A93" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:6">
@@ -3216,7 +3216,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
         <x:v>102</x:v>
@@ -3230,10 +3230,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
         <x:v>97</x:v>
@@ -3253,18 +3253,18 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:6">
       <x:c r="A100" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>99</x:v>
@@ -3276,7 +3276,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
         <x:v>104</x:v>
@@ -3287,7 +3287,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
         <x:v>99</x:v>
@@ -3295,7 +3295,7 @@
     </x:row>
     <x:row r="103" spans="1:6">
       <x:c r="A103" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:6">
@@ -3323,16 +3323,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
         <x:v>105</x:v>
@@ -3349,7 +3349,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
         <x:v>102</x:v>
@@ -3363,7 +3363,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>103</x:v>
@@ -3420,7 +3420,7 @@
     </x:row>
     <x:row r="110" spans="1:6">
       <x:c r="A110" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>104</x:v>
@@ -3445,7 +3445,7 @@
     </x:row>
     <x:row r="113" spans="1:6">
       <x:c r="A113" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:6">
@@ -3473,10 +3473,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
         <x:v>108</x:v>
@@ -3487,7 +3487,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>100</x:v>
@@ -3499,7 +3499,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:6">
@@ -3564,7 +3564,7 @@
     </x:row>
     <x:row r="120" spans="1:6">
       <x:c r="A120" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>102</x:v>
@@ -3666,7 +3666,7 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
         <x:v>129</x:v>
@@ -3677,16 +3677,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="E128" s="0" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
         <x:v>131</x:v>
@@ -3697,10 +3697,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>129</x:v>
@@ -3714,13 +3714,13 @@
     </x:row>
     <x:row r="130" spans="1:6">
       <x:c r="A130" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>125</x:v>
@@ -3737,18 +3737,18 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:6">
       <x:c r="A133" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:6">
@@ -3776,7 +3776,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>126</x:v>
@@ -3785,7 +3785,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
         <x:v>130</x:v>
@@ -3799,13 +3799,13 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
         <x:v>129</x:v>
@@ -3819,16 +3819,16 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:6">
@@ -3848,7 +3848,7 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:6">
@@ -3862,24 +3862,24 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:6">
       <x:c r="A140" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>130</x:v>
@@ -3932,7 +3932,7 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
         <x:v>129</x:v>
@@ -3943,13 +3943,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
         <x:v>126</x:v>
@@ -3966,10 +3966,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
         <x:v>129</x:v>
@@ -3983,19 +3983,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:6">
@@ -4009,7 +4009,7 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
         <x:v>130</x:v>
@@ -4020,10 +4020,10 @@
     </x:row>
     <x:row r="150" spans="1:6">
       <x:c r="A150" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
         <x:v>130</x:v>
@@ -4032,7 +4032,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
         <x:v>142</x:v>
@@ -4043,16 +4043,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
         <x:v>128</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:6">
@@ -4088,7 +4088,7 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>129</x:v>
@@ -4108,13 +4108,13 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E156" s="0" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="E156" s="0" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
         <x:v>131</x:v>
@@ -4134,10 +4134,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:6">
@@ -4148,16 +4148,16 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:6">
@@ -4165,7 +4165,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
         <x:v>130</x:v>
@@ -4182,7 +4182,7 @@
     </x:row>
     <x:row r="160" spans="1:6">
       <x:c r="A160" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>128</x:v>
@@ -4191,7 +4191,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
         <x:v>130</x:v>
@@ -4318,7 +4318,7 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="E169" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
         <x:v>150</x:v>
@@ -4326,10 +4326,10 @@
     </x:row>
     <x:row r="170" spans="1:6">
       <x:c r="A170" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C170" s="0" t="s">
         <x:v>162</x:v>
@@ -4338,7 +4338,7 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="E170" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
         <x:v>153</x:v>
@@ -4431,10 +4431,10 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="C177" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="D177" s="0" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="E177" s="0" t="s">
         <x:v>156</x:v>
@@ -4454,10 +4454,10 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="E178" s="0" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="E178" s="0" t="s">
-        <x:v>156</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
         <x:v>153</x:v>
@@ -4468,10 +4468,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C179" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>158</x:v>
@@ -4485,7 +4485,7 @@
     </x:row>
     <x:row r="180" spans="1:6">
       <x:c r="A180" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>153</x:v>
@@ -4519,7 +4519,7 @@
     </x:row>
     <x:row r="183" spans="1:6">
       <x:c r="A183" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:6">
@@ -4547,7 +4547,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C185" s="0" t="s">
         <x:v>153</x:v>
@@ -4556,7 +4556,7 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="E185" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F185" s="0" t="s">
         <x:v>157</x:v>
@@ -4576,7 +4576,7 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="E186" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F186" s="0" t="s">
         <x:v>161</x:v>
@@ -4607,16 +4607,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C188" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
         <x:v>153</x:v>
       </x:c>
       <x:c r="E188" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F188" s="0" t="s">
         <x:v>150</x:v>
@@ -4636,15 +4636,15 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="E189" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="F189" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:6">
       <x:c r="A190" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>158</x:v>
@@ -4718,7 +4718,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="F195" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:6">
@@ -4746,7 +4746,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C197" s="0" t="s">
         <x:v>162</x:v>
@@ -4755,7 +4755,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="E197" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F197" s="0" t="s">
         <x:v>157</x:v>
@@ -4778,7 +4778,7 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="F198" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:6">
@@ -4803,7 +4803,7 @@
     </x:row>
     <x:row r="200" spans="1:6">
       <x:c r="A200" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>156</x:v>
@@ -4823,10 +4823,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C201" s="0" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="C201" s="0" t="s">
-        <x:v>159</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
         <x:v>162</x:v>
@@ -4959,7 +4959,7 @@
     </x:row>
     <x:row r="210" spans="1:6">
       <x:c r="A210" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>192</x:v>
@@ -4982,15 +4982,15 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C211" s="0" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="C211" s="0" t="s">
-        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:6">
       <x:c r="A213" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:6">
@@ -5018,7 +5018,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C215" s="0" t="s">
         <x:v>192</x:v>
@@ -5047,7 +5047,7 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="F216" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:6">
@@ -5064,7 +5064,7 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="E217" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F217" s="0" t="s">
         <x:v>191</x:v>
@@ -5098,7 +5098,7 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="C219" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
         <x:v>185</x:v>
@@ -5107,12 +5107,12 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="F219" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:6">
       <x:c r="A220" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>178</x:v>
@@ -5229,7 +5229,7 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="F227" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="228" spans="1:6">
@@ -5237,7 +5237,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C228" s="0" t="s">
         <x:v>182</x:v>
@@ -5274,7 +5274,7 @@
     </x:row>
     <x:row r="230" spans="1:6">
       <x:c r="A230" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>185</x:v>
@@ -5342,7 +5342,7 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="E235" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F235" s="0" t="s">
         <x:v>178</x:v>
@@ -5402,10 +5402,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="E238" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F238" s="0" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="F238" s="0" t="s">
-        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="239" spans="1:6">
@@ -5419,7 +5419,7 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="D239" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E239" s="0" t="s">
         <x:v>187</x:v>
@@ -5430,7 +5430,7 @@
     </x:row>
     <x:row r="240" spans="1:6">
       <x:c r="A240" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>183</x:v>
@@ -5456,7 +5456,7 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="D241" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8228,19 +8228,19 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
         <x:v>276</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:6">
@@ -8248,19 +8248,19 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
         <x:v>276</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:6">
@@ -8308,10 +8308,10 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>220</x:v>
@@ -8320,7 +8320,7 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:6">
@@ -8331,7 +8331,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>220</x:v>
@@ -8340,7 +8340,7 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:6">
@@ -8391,7 +8391,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
         <x:v>238</x:v>
@@ -8400,7 +8400,7 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:6">
@@ -8411,16 +8411,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
         <x:v>278</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:6">
@@ -8431,7 +8431,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>236</x:v>
@@ -8440,7 +8440,7 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:6">
@@ -8448,19 +8448,19 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
         <x:v>278</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:6">
@@ -8471,16 +8471,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
         <x:v>278</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:6">
@@ -8788,7 +8788,7 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C166" s="0">
         <x:v>7</x:v>
@@ -9231,16 +9231,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E188" s="0" t="s">
         <x:v>287</x:v>
       </x:c>
       <x:c r="F188" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:6">
@@ -9251,16 +9251,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C189" s="0">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E189" s="0" t="s">
         <x:v>287</x:v>
       </x:c>
       <x:c r="F189" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:6">
@@ -9268,19 +9268,19 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C190" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E190" s="0" t="s">
         <x:v>287</x:v>
       </x:c>
       <x:c r="F190" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:6">
@@ -9788,19 +9788,19 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C216" s="0">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E216" s="0" t="s">
         <x:v>287</x:v>
       </x:c>
       <x:c r="F216" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:6">
@@ -9811,16 +9811,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C217" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E217" s="0" t="s">
         <x:v>287</x:v>
       </x:c>
       <x:c r="F217" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:6">
@@ -9831,16 +9831,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C218" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E218" s="0" t="s">
         <x:v>287</x:v>
       </x:c>
       <x:c r="F218" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:6">
@@ -10348,10 +10348,10 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C244" s="0">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D244" s="0" t="s">
         <x:v>220</x:v>
@@ -10911,16 +10911,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C272" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D272" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E272" s="0" t="s">
         <x:v>309</x:v>
       </x:c>
       <x:c r="F272" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="273" spans="1:6">
@@ -10928,19 +10928,19 @@
         <x:v>308</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C273" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D273" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E273" s="0" t="s">
         <x:v>309</x:v>
       </x:c>
       <x:c r="F273" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="274" spans="1:6">
@@ -13528,19 +13528,19 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C403" s="0">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D403" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E403" s="0" t="s">
         <x:v>352</x:v>
       </x:c>
       <x:c r="F403" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="404" spans="1:6">
@@ -13548,19 +13548,19 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C404" s="0">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D404" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E404" s="0" t="s">
         <x:v>352</x:v>
       </x:c>
       <x:c r="F404" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="405" spans="1:6">
@@ -14531,7 +14531,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C453" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D453" s="0" t="s">
         <x:v>230</x:v>
@@ -14540,7 +14540,7 @@
         <x:v>385</x:v>
       </x:c>
       <x:c r="F453" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="454" spans="1:6">
@@ -14551,16 +14551,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C454" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D454" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E454" s="0" t="s">
         <x:v>385</x:v>
       </x:c>
       <x:c r="F454" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="455" spans="1:6">
@@ -14568,19 +14568,19 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="B455" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C455" s="0">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D455" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E455" s="0" t="s">
         <x:v>385</x:v>
       </x:c>
       <x:c r="F455" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="456" spans="1:6">
@@ -14588,7 +14588,7 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="B456" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C456" s="0">
         <x:v>3</x:v>
@@ -14600,7 +14600,7 @@
         <x:v>385</x:v>
       </x:c>
       <x:c r="F456" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="457" spans="1:6">
@@ -14611,10 +14611,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C457" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D457" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E457" s="0" t="s">
         <x:v>385</x:v>
@@ -14631,7 +14631,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C458" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D458" s="0" t="s">
         <x:v>209</x:v>
@@ -14640,7 +14640,7 @@
         <x:v>385</x:v>
       </x:c>
       <x:c r="F458" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:6">
@@ -14651,16 +14651,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C459" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D459" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E459" s="0" t="s">
         <x:v>385</x:v>
       </x:c>
       <x:c r="F459" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="460" spans="1:6">
@@ -14668,19 +14668,19 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="B460" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C460" s="0">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D460" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E460" s="0" t="s">
         <x:v>385</x:v>
       </x:c>
       <x:c r="F460" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="461" spans="1:6">
@@ -14691,16 +14691,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C461" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D461" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E461" s="0" t="s">
         <x:v>385</x:v>
       </x:c>
       <x:c r="F461" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="462" spans="1:6">
@@ -16591,7 +16591,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C556" s="0">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D556" s="0" t="s">
         <x:v>271</x:v>
@@ -17211,16 +17211,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C587" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D587" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E587" s="0" t="s">
         <x:v>405</x:v>
       </x:c>
       <x:c r="F587" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="588" spans="1:6">
@@ -17231,16 +17231,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C588" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D588" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E588" s="0" t="s">
         <x:v>405</x:v>
       </x:c>
       <x:c r="F588" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:6">
@@ -17248,10 +17248,10 @@
         <x:v>407</x:v>
       </x:c>
       <x:c r="B589" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C589" s="0">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D589" s="0" t="s">
         <x:v>240</x:v>
@@ -17260,7 +17260,7 @@
         <x:v>405</x:v>
       </x:c>
       <x:c r="F589" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:6">
@@ -18668,10 +18668,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B660" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C660" s="0">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D660" s="0" t="s">
         <x:v>265</x:v>
@@ -18691,16 +18691,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C661" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D661" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E661" s="0" t="s">
         <x:v>413</x:v>
       </x:c>
       <x:c r="F661" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:6">
@@ -18708,19 +18708,19 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B662" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C662" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D662" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E662" s="0" t="s">
         <x:v>413</x:v>
       </x:c>
       <x:c r="F662" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:6">
@@ -18728,7 +18728,7 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B663" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C663" s="0">
         <x:v>4</x:v>
@@ -18748,19 +18748,19 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B664" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C664" s="0">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D664" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E664" s="0" t="s">
         <x:v>413</x:v>
       </x:c>
       <x:c r="F664" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:6">
@@ -18771,16 +18771,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C665" s="0">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D665" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E665" s="0" t="s">
         <x:v>413</x:v>
       </x:c>
       <x:c r="F665" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:6">
@@ -20088,19 +20088,19 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B731" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C731" s="0">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D731" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E731" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
       <x:c r="F731" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:6">
@@ -20111,16 +20111,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C732" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D732" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E732" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
       <x:c r="F732" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:6">
@@ -20128,10 +20128,10 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B733" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C733" s="0">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D733" s="0" t="s">
         <x:v>220</x:v>
@@ -20140,7 +20140,7 @@
         <x:v>432</x:v>
       </x:c>
       <x:c r="F733" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:6">
@@ -20151,7 +20151,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C734" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D734" s="0" t="s">
         <x:v>220</x:v>
@@ -20160,7 +20160,7 @@
         <x:v>432</x:v>
       </x:c>
       <x:c r="F734" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:6">
@@ -20168,10 +20168,10 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B735" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C735" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D735" s="0" t="s">
         <x:v>220</x:v>
@@ -20288,7 +20288,7 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="B741" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C741" s="0">
         <x:v>2</x:v>
@@ -20311,16 +20311,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C742" s="0">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D742" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E742" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
       <x:c r="F742" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:6">
@@ -20328,19 +20328,19 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B743" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C743" s="0">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D743" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E743" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
       <x:c r="F743" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="744" spans="1:6">
@@ -20351,10 +20351,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C744" s="0">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D744" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E744" s="0" t="s">
         <x:v>432</x:v>
@@ -20371,16 +20371,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C745" s="0">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D745" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E745" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
       <x:c r="F745" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:6">
@@ -20391,16 +20391,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C746" s="0">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D746" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E746" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
       <x:c r="F746" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:6">
@@ -20408,19 +20408,19 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B747" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C747" s="0">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D747" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="E747" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
       <x:c r="F747" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:6">
@@ -20428,19 +20428,19 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B748" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C748" s="0">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D748" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E748" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
       <x:c r="F748" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:6">
@@ -20448,19 +20448,19 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B749" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C749" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D749" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="E749" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
       <x:c r="F749" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:6">
@@ -21088,7 +21088,7 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="B781" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C781" s="0">
         <x:v>2</x:v>
@@ -21911,16 +21911,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C822" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D822" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E822" s="0" t="s">
         <x:v>438</x:v>
       </x:c>
       <x:c r="F822" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="823" spans="1:6">
@@ -21931,7 +21931,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C823" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D823" s="0" t="s">
         <x:v>264</x:v>
@@ -21940,7 +21940,7 @@
         <x:v>438</x:v>
       </x:c>
       <x:c r="F823" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="824" spans="1:6">
@@ -21948,19 +21948,19 @@
         <x:v>444</x:v>
       </x:c>
       <x:c r="B824" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C824" s="0">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D824" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E824" s="0" t="s">
         <x:v>438</x:v>
       </x:c>
       <x:c r="F824" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="825" spans="1:6">
@@ -21971,16 +21971,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C825" s="0">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D825" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E825" s="0" t="s">
         <x:v>438</x:v>
       </x:c>
       <x:c r="F825" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="826" spans="1:6">
@@ -21991,16 +21991,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C826" s="0">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D826" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E826" s="0" t="s">
         <x:v>438</x:v>
       </x:c>
       <x:c r="F826" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="827" spans="1:6">
@@ -22008,13 +22008,13 @@
         <x:v>444</x:v>
       </x:c>
       <x:c r="B827" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C827" s="0">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D827" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E827" s="0" t="s">
         <x:v>438</x:v>
@@ -22028,19 +22028,19 @@
         <x:v>444</x:v>
       </x:c>
       <x:c r="B828" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C828" s="0">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D828" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E828" s="0" t="s">
         <x:v>438</x:v>
       </x:c>
       <x:c r="F828" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="829" spans="1:6">
@@ -22588,7 +22588,7 @@
         <x:v>454</x:v>
       </x:c>
       <x:c r="B856" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C856" s="0">
         <x:v>4</x:v>
@@ -22608,7 +22608,7 @@
         <x:v>454</x:v>
       </x:c>
       <x:c r="B857" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C857" s="0">
         <x:v>4</x:v>
@@ -22991,16 +22991,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C876" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D876" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E876" s="0" t="s">
         <x:v>453</x:v>
       </x:c>
       <x:c r="F876" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="877" spans="1:6">
@@ -23011,16 +23011,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C877" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D877" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E877" s="0" t="s">
         <x:v>453</x:v>
       </x:c>
       <x:c r="F877" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="878" spans="1:6">
@@ -23341,10 +23341,10 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -23781,10 +23781,10 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>454</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
@@ -24241,10 +24241,10 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -24921,10 +24921,10 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>418</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:6">
@@ -25161,10 +25161,10 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>444</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:6">
@@ -25681,10 +25681,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>434</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:6">
@@ -26581,10 +26581,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="E169" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>353</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:6">
@@ -28041,10 +28041,10 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="E242" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F242" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>418</x:v>
       </x:c>
     </x:row>
     <x:row r="243" spans="1:6">
@@ -28701,10 +28701,10 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="E275" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="F275" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>444</x:v>
       </x:c>
     </x:row>
     <x:row r="276" spans="1:6">
@@ -32141,10 +32141,10 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="E447" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F447" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="448" spans="1:6">
@@ -32361,10 +32361,10 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="E458" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F458" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:6">
@@ -33701,10 +33701,10 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="E525" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="F525" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:6">
@@ -33861,10 +33861,10 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="E533" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F533" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>433</x:v>
       </x:c>
     </x:row>
     <x:row r="534" spans="1:6">
@@ -36335,16 +36335,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C657" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D657" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E657" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F657" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:6">
@@ -36355,16 +36355,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C658" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D658" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E658" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F658" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:6">
@@ -36375,16 +36375,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C659" s="0">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D659" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E659" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F659" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>412</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:6">
@@ -36395,16 +36395,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C660" s="0">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D660" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E660" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="F660" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>391</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:6">
@@ -36415,16 +36415,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C661" s="0">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D661" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E661" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="F661" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:6">
@@ -36435,16 +36435,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C662" s="0">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D662" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E662" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="F662" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:6">
@@ -36452,19 +36452,19 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="B663" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C663" s="0">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D663" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E663" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="F663" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>358</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:6">
@@ -36475,16 +36475,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C664" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D664" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E664" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F664" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:6">
@@ -36495,16 +36495,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C665" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D665" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E665" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="F665" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:6">
@@ -37655,16 +37655,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C723" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D723" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E723" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="F723" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:6">
@@ -37675,16 +37675,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C724" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D724" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E724" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F724" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:6">
@@ -37695,16 +37695,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C725" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D725" s="0" t="s">
         <x:v>236</x:v>
       </x:c>
       <x:c r="E725" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F725" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>415</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:6">
@@ -37715,16 +37715,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C726" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D726" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E726" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F726" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:6">
@@ -37735,16 +37735,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C727" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D727" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E727" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="F727" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:6">
@@ -37755,16 +37755,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C728" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D728" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E728" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F728" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:6">
@@ -37772,19 +37772,19 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="B729" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C729" s="0">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D729" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E729" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F729" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:6">
@@ -37795,16 +37795,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C730" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D730" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E730" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F730" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>407</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:6">
@@ -38101,10 +38101,10 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="E745" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F745" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:6">
@@ -38421,10 +38421,10 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="E761" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F761" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:6">
@@ -38441,10 +38441,10 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="E762" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F762" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>431</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:6">
@@ -38541,10 +38541,10 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="E767" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F767" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>431</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:6">
@@ -39172,19 +39172,19 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B799" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C799" s="0">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D799" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E799" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F799" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="800" spans="1:6">
@@ -39195,16 +39195,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C800" s="0">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D800" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E800" s="0" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="F800" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="801" spans="1:6">
@@ -39215,16 +39215,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C801" s="0">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D801" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E801" s="0" t="s">
         <x:v>221</x:v>
       </x:c>
       <x:c r="F801" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="802" spans="1:6">
@@ -39235,16 +39235,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C802" s="0">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D802" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E802" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="F802" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="803" spans="1:6">
@@ -39255,16 +39255,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C803" s="0">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D803" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E803" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F803" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="804" spans="1:6">
@@ -40732,19 +40732,19 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B877" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C877" s="0">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D877" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E877" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F877" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="878" spans="1:6">
@@ -40755,16 +40755,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C878" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D878" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E878" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F878" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="879" spans="1:6">
